--- a/Daily_Report/Top 7 broker List with its Turnover 2024-02-07.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-02-07.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="278">
   <si>
     <t>Date: 2024-02-07</t>
   </si>
@@ -59,109 +59,109 @@
     <t>7</t>
   </si>
   <si>
-    <t>Naasa Securities Co. Ltd.</t>
+    <t>Imperial Securities Co .Pvt.Limited</t>
+  </si>
+  <si>
+    <t>Sani Securities Company Limited</t>
+  </si>
+  <si>
+    <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
+  </si>
+  <si>
+    <t>Vision Securities Pvt.Limited</t>
+  </si>
+  <si>
+    <t>Nepal Investment &amp; Securities Trading Pvt. Limited</t>
+  </si>
+  <si>
+    <t>Kohinoor Investment and Securities Pvt.Ltd</t>
   </si>
   <si>
     <t>Dynamic Money Managers Securities Pvt.Ltd</t>
   </si>
   <si>
-    <t>Vision Securities Pvt.Limited</t>
-  </si>
-  <si>
-    <t>Imperial Securities Co .Pvt.Limited</t>
-  </si>
-  <si>
-    <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
-  </si>
-  <si>
-    <t>Sani Securities Company Limited</t>
-  </si>
-  <si>
-    <t>Online Securities Pvt.Ltd</t>
-  </si>
-  <si>
-    <t>58</t>
+    <t>45</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>35</t>
   </si>
   <si>
     <t>44</t>
   </si>
   <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>330,167,299.1</t>
-  </si>
-  <si>
-    <t>240,167,572.66</t>
-  </si>
-  <si>
-    <t>237,133,273.0</t>
-  </si>
-  <si>
-    <t>223,659,547.89</t>
-  </si>
-  <si>
-    <t>214,726,546.1</t>
-  </si>
-  <si>
-    <t>203,228,492.6</t>
-  </si>
-  <si>
-    <t>180,329,660.05</t>
-  </si>
-  <si>
-    <t>156,636,196.4</t>
-  </si>
-  <si>
-    <t>124,611,225.06</t>
-  </si>
-  <si>
-    <t>133,406,767.6</t>
-  </si>
-  <si>
-    <t>113,586,386.6</t>
-  </si>
-  <si>
-    <t>98,888,914.3</t>
-  </si>
-  <si>
-    <t>104,732,670.0</t>
-  </si>
-  <si>
-    <t>103,417,149.35</t>
-  </si>
-  <si>
-    <t>173,531,102.7</t>
-  </si>
-  <si>
-    <t>115,556,347.6</t>
-  </si>
-  <si>
-    <t>103,726,505.4</t>
-  </si>
-  <si>
-    <t>110,073,161.3</t>
-  </si>
-  <si>
-    <t>115,837,631.8</t>
-  </si>
-  <si>
-    <t>98,495,822.6</t>
-  </si>
-  <si>
-    <t>76,912,510.7</t>
+    <t>404,956,357.2</t>
+  </si>
+  <si>
+    <t>306,797,368.0</t>
+  </si>
+  <si>
+    <t>271,124,483.7</t>
+  </si>
+  <si>
+    <t>266,533,214.5</t>
+  </si>
+  <si>
+    <t>248,747,393.9</t>
+  </si>
+  <si>
+    <t>246,051,657.25</t>
+  </si>
+  <si>
+    <t>243,639,597.56</t>
+  </si>
+  <si>
+    <t>86,948,524.9</t>
+  </si>
+  <si>
+    <t>136,283,223.3</t>
+  </si>
+  <si>
+    <t>165,696,972.69</t>
+  </si>
+  <si>
+    <t>161,493,626.5</t>
+  </si>
+  <si>
+    <t>157,006,038.8</t>
+  </si>
+  <si>
+    <t>170,038,217.69</t>
+  </si>
+  <si>
+    <t>101,757,792.76</t>
+  </si>
+  <si>
+    <t>318,007,832.3</t>
+  </si>
+  <si>
+    <t>170,514,144.69</t>
+  </si>
+  <si>
+    <t>105,427,511.0</t>
+  </si>
+  <si>
+    <t>105,039,588.0</t>
+  </si>
+  <si>
+    <t>91,741,355.1</t>
+  </si>
+  <si>
+    <t>76,013,439.55</t>
+  </si>
+  <si>
+    <t>141,881,804.8</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -179,448 +179,463 @@
     <t>% of turnover</t>
   </si>
   <si>
-    <t>MAKAR</t>
-  </si>
-  <si>
-    <t>9,925,105.0</t>
+    <t>SONA</t>
+  </si>
+  <si>
+    <t>30,960,560.0</t>
+  </si>
+  <si>
+    <t>NGPL</t>
+  </si>
+  <si>
+    <t>18,544,520.0</t>
+  </si>
+  <si>
+    <t>MKHC</t>
+  </si>
+  <si>
+    <t>16,366,359.3</t>
+  </si>
+  <si>
+    <t>SHL</t>
+  </si>
+  <si>
+    <t>3,969,970.0</t>
+  </si>
+  <si>
+    <t>HRL</t>
+  </si>
+  <si>
+    <t>1,935,042.0</t>
+  </si>
+  <si>
+    <t>40,017,087.79</t>
+  </si>
+  <si>
+    <t>NRIC</t>
+  </si>
+  <si>
+    <t>22,086,222.8</t>
+  </si>
+  <si>
+    <t>KSBBL</t>
+  </si>
+  <si>
+    <t>19,440,000.0</t>
+  </si>
+  <si>
+    <t>15,161,138.0</t>
+  </si>
+  <si>
+    <t>KKHC</t>
+  </si>
+  <si>
+    <t>10,854,240.0</t>
+  </si>
+  <si>
+    <t>TRH</t>
+  </si>
+  <si>
+    <t>52,845,210.0</t>
+  </si>
+  <si>
+    <t>HDHPC</t>
+  </si>
+  <si>
+    <t>33,373,914.6</t>
+  </si>
+  <si>
+    <t>29,317,505.7</t>
+  </si>
+  <si>
+    <t>NLIC</t>
+  </si>
+  <si>
+    <t>18,858,614.0</t>
+  </si>
+  <si>
+    <t>12,463,200.0</t>
+  </si>
+  <si>
+    <t>SMJC</t>
+  </si>
+  <si>
+    <t>40,329,900.0</t>
+  </si>
+  <si>
+    <t>37,446,163.0</t>
+  </si>
+  <si>
+    <t>USHEC</t>
+  </si>
+  <si>
+    <t>36,314,376.8</t>
+  </si>
+  <si>
+    <t>SAHAS</t>
+  </si>
+  <si>
+    <t>20,576,508.0</t>
+  </si>
+  <si>
+    <t>3,454,028.3</t>
+  </si>
+  <si>
+    <t>119,991,000.0</t>
+  </si>
+  <si>
+    <t>SCB</t>
+  </si>
+  <si>
+    <t>17,539,144.0</t>
+  </si>
+  <si>
+    <t>GFCL</t>
+  </si>
+  <si>
+    <t>11,869,200.0</t>
   </si>
   <si>
     <t>HATHY</t>
   </si>
   <si>
-    <t>9,093,671.69</t>
-  </si>
-  <si>
-    <t>NGPL</t>
-  </si>
-  <si>
-    <t>9,009,240.8</t>
-  </si>
-  <si>
-    <t>NRN</t>
-  </si>
-  <si>
-    <t>8,485,679.0</t>
-  </si>
-  <si>
-    <t>UNHPL</t>
-  </si>
-  <si>
-    <t>5,556,104.6</t>
+    <t>2,280,060.5</t>
+  </si>
+  <si>
+    <t>693,558.0</t>
+  </si>
+  <si>
+    <t>SNLI</t>
+  </si>
+  <si>
+    <t>66,942,720.0</t>
+  </si>
+  <si>
+    <t>IHL</t>
+  </si>
+  <si>
+    <t>38,050,568.0</t>
+  </si>
+  <si>
+    <t>RHGCL</t>
+  </si>
+  <si>
+    <t>32,441,470.0</t>
+  </si>
+  <si>
+    <t>GCIL</t>
+  </si>
+  <si>
+    <t>11,098,080.0</t>
+  </si>
+  <si>
+    <t>MHCL</t>
+  </si>
+  <si>
+    <t>3,780,498.0</t>
+  </si>
+  <si>
+    <t>DDBL</t>
+  </si>
+  <si>
+    <t>54,397,479.0</t>
+  </si>
+  <si>
+    <t>RBCL</t>
+  </si>
+  <si>
+    <t>15,176,268.0</t>
   </si>
   <si>
     <t>RNLI</t>
   </si>
   <si>
-    <t>38,252,825.2</t>
-  </si>
-  <si>
-    <t>HRL</t>
-  </si>
-  <si>
-    <t>20,826,097.89</t>
-  </si>
-  <si>
-    <t>SHPC</t>
-  </si>
-  <si>
-    <t>4,657,510.5</t>
-  </si>
-  <si>
-    <t>SONA</t>
-  </si>
-  <si>
-    <t>4,178,023.0</t>
-  </si>
-  <si>
-    <t>NTC</t>
-  </si>
-  <si>
-    <t>2,531,041.0</t>
-  </si>
-  <si>
-    <t>SHINE</t>
-  </si>
-  <si>
-    <t>9,839,587.9</t>
-  </si>
-  <si>
-    <t>KSBBL</t>
-  </si>
-  <si>
-    <t>6,176,473.0</t>
-  </si>
-  <si>
-    <t>MHNL</t>
-  </si>
-  <si>
-    <t>5,937,396.0</t>
-  </si>
-  <si>
-    <t>5,546,243.0</t>
-  </si>
-  <si>
-    <t>5,253,723.0</t>
-  </si>
-  <si>
-    <t>8,054,593.6</t>
-  </si>
-  <si>
-    <t>SHL</t>
-  </si>
-  <si>
-    <t>7,398,254.0</t>
-  </si>
-  <si>
-    <t>PROFLP</t>
-  </si>
-  <si>
-    <t>6,130,342.0</t>
-  </si>
-  <si>
-    <t>PPL</t>
-  </si>
-  <si>
-    <t>5,582,507.0</t>
-  </si>
-  <si>
-    <t>SHIVM</t>
-  </si>
-  <si>
-    <t>5,173,504.0</t>
-  </si>
-  <si>
-    <t>10,376,527.69</t>
-  </si>
-  <si>
-    <t>4,242,000.0</t>
-  </si>
-  <si>
-    <t>HDHPC</t>
-  </si>
-  <si>
-    <t>3,954,683.0</t>
-  </si>
-  <si>
-    <t>3,954,251.9</t>
-  </si>
-  <si>
-    <t>NRIC</t>
-  </si>
-  <si>
-    <t>3,373,343.0</t>
-  </si>
-  <si>
-    <t>9,120,719.3</t>
-  </si>
-  <si>
-    <t>4,581,299.0</t>
+    <t>11,772,496.0</t>
+  </si>
+  <si>
+    <t>7,161,027.4</t>
+  </si>
+  <si>
+    <t>UAIL</t>
+  </si>
+  <si>
+    <t>2,599,680.0</t>
+  </si>
+  <si>
+    <t>Sell Amount</t>
+  </si>
+  <si>
+    <t>226,389,490.5</t>
+  </si>
+  <si>
+    <t>DORDI</t>
+  </si>
+  <si>
+    <t>47,105,780.0</t>
+  </si>
+  <si>
+    <t>UMRH</t>
+  </si>
+  <si>
+    <t>10,238,400.0</t>
+  </si>
+  <si>
+    <t>8,803,069.0</t>
+  </si>
+  <si>
+    <t>SJLIC</t>
+  </si>
+  <si>
+    <t>3,849,074.59</t>
+  </si>
+  <si>
+    <t>55,738,097.2</t>
+  </si>
+  <si>
+    <t>19,977,030.0</t>
+  </si>
+  <si>
+    <t>18,685,700.0</t>
+  </si>
+  <si>
+    <t>NHPC</t>
+  </si>
+  <si>
+    <t>18,254,160.0</t>
+  </si>
+  <si>
+    <t>8,014,815.1</t>
+  </si>
+  <si>
+    <t>39,110,553.0</t>
+  </si>
+  <si>
+    <t>NIMB</t>
+  </si>
+  <si>
+    <t>27,702,000.0</t>
+  </si>
+  <si>
+    <t>AKJCL</t>
+  </si>
+  <si>
+    <t>16,648,956.0</t>
+  </si>
+  <si>
+    <t>UPPER</t>
+  </si>
+  <si>
+    <t>4,507,040.0</t>
+  </si>
+  <si>
+    <t>2,469,911.0</t>
+  </si>
+  <si>
+    <t>UPCL</t>
+  </si>
+  <si>
+    <t>22,484,710.0</t>
+  </si>
+  <si>
+    <t>CLI</t>
+  </si>
+  <si>
+    <t>18,289,881.0</t>
+  </si>
+  <si>
+    <t>HDL</t>
+  </si>
+  <si>
+    <t>9,280,786.69</t>
+  </si>
+  <si>
+    <t>8,974,756.8</t>
+  </si>
+  <si>
+    <t>5,536,670.0</t>
+  </si>
+  <si>
+    <t>38,287,080.0</t>
+  </si>
+  <si>
+    <t>18,157,770.0</t>
+  </si>
+  <si>
+    <t>NMB50</t>
+  </si>
+  <si>
+    <t>12,888,720.0</t>
+  </si>
+  <si>
+    <t>11,671,361.3</t>
+  </si>
+  <si>
+    <t>NWCL</t>
+  </si>
+  <si>
+    <t>1,156,148.5</t>
+  </si>
+  <si>
+    <t>30,848,744.0</t>
+  </si>
+  <si>
+    <t>15,404,861.0</t>
   </si>
   <si>
     <t>ILI</t>
   </si>
   <si>
-    <t>4,030,418.0</t>
-  </si>
-  <si>
-    <t>3,688,101.9</t>
-  </si>
-  <si>
-    <t>3,641,219.0</t>
-  </si>
-  <si>
-    <t>8,000,692.0</t>
-  </si>
-  <si>
-    <t>4,795,974.0</t>
-  </si>
-  <si>
-    <t>CIT</t>
-  </si>
-  <si>
-    <t>4,535,469.0</t>
-  </si>
-  <si>
-    <t>4,434,187.0</t>
-  </si>
-  <si>
-    <t>CLI</t>
-  </si>
-  <si>
-    <t>3,947,094.9</t>
-  </si>
-  <si>
-    <t>Sell Amount</t>
+    <t>8,038,753.0</t>
+  </si>
+  <si>
+    <t>NIFRA</t>
+  </si>
+  <si>
+    <t>2,381,976.4</t>
+  </si>
+  <si>
+    <t>2,237,782.0</t>
+  </si>
+  <si>
+    <t>54,220,752.0</t>
+  </si>
+  <si>
+    <t>30,913,388.8</t>
+  </si>
+  <si>
+    <t>MBL</t>
+  </si>
+  <si>
+    <t>20,893,952.1</t>
+  </si>
+  <si>
+    <t>17,740,450.0</t>
+  </si>
+  <si>
+    <t>7,994,483.0</t>
+  </si>
+  <si>
+    <t>Top Traded Stocks</t>
+  </si>
+  <si>
+    <t>Turnover (Rs.)</t>
+  </si>
+  <si>
+    <t>Sub Indices</t>
+  </si>
+  <si>
+    <t>Turnover</t>
+  </si>
+  <si>
+    <t>Percentage (%)</t>
+  </si>
+  <si>
+    <t>236,445,141.0</t>
+  </si>
+  <si>
+    <t>231,489,472.9</t>
+  </si>
+  <si>
+    <t>204,230,414.8</t>
   </si>
   <si>
     <t>MEN</t>
   </si>
   <si>
-    <t>14,785,158.0</t>
-  </si>
-  <si>
-    <t>10,514,277.9</t>
-  </si>
-  <si>
-    <t>9,848,083.4</t>
-  </si>
-  <si>
-    <t>UAIL</t>
-  </si>
-  <si>
-    <t>6,627,561.2</t>
-  </si>
-  <si>
-    <t>SAHAS</t>
-  </si>
-  <si>
-    <t>6,006,831.5</t>
-  </si>
-  <si>
-    <t>42,207,256.29</t>
-  </si>
-  <si>
-    <t>6,167,305.5</t>
-  </si>
-  <si>
-    <t>4,669,795.0</t>
-  </si>
-  <si>
-    <t>SWBBL</t>
-  </si>
-  <si>
-    <t>4,277,702.09</t>
-  </si>
-  <si>
-    <t>AKPL</t>
-  </si>
-  <si>
-    <t>3,838,186.8</t>
-  </si>
-  <si>
-    <t>7,931,371.5</t>
-  </si>
-  <si>
-    <t>HPPL</t>
-  </si>
-  <si>
-    <t>5,843,039.8</t>
-  </si>
-  <si>
-    <t>5,757,637.2</t>
-  </si>
-  <si>
-    <t>RIDI</t>
-  </si>
-  <si>
-    <t>4,037,968.3</t>
-  </si>
-  <si>
-    <t>HURJA</t>
-  </si>
-  <si>
-    <t>3,982,425.0</t>
-  </si>
-  <si>
-    <t>14,756,459.6</t>
-  </si>
-  <si>
-    <t>DORDI</t>
-  </si>
-  <si>
-    <t>6,978,300.5</t>
-  </si>
-  <si>
-    <t>SMJC</t>
-  </si>
-  <si>
-    <t>4,972,274.09</t>
-  </si>
-  <si>
-    <t>CGH</t>
-  </si>
-  <si>
-    <t>4,861,777.0</t>
-  </si>
-  <si>
-    <t>3,648,204.0</t>
-  </si>
-  <si>
-    <t>53,170,031.7</t>
-  </si>
-  <si>
-    <t>2,509,379.29</t>
-  </si>
-  <si>
-    <t>LEC</t>
-  </si>
-  <si>
-    <t>2,167,816.0</t>
-  </si>
-  <si>
-    <t>2,151,305.5</t>
-  </si>
-  <si>
-    <t>BARUN</t>
-  </si>
-  <si>
-    <t>1,991,835.6</t>
-  </si>
-  <si>
-    <t>10,929,468.0</t>
-  </si>
-  <si>
-    <t>ALICL</t>
-  </si>
-  <si>
-    <t>6,813,695.9</t>
-  </si>
-  <si>
-    <t>6,018,578.4</t>
-  </si>
-  <si>
-    <t>4,384,615.5</t>
-  </si>
-  <si>
-    <t>4,015,081.3</t>
-  </si>
-  <si>
-    <t>LSL</t>
-  </si>
-  <si>
-    <t>5,306,300.2</t>
-  </si>
-  <si>
-    <t>5,210,031.0</t>
-  </si>
-  <si>
-    <t>4,776,146.2</t>
-  </si>
-  <si>
-    <t>2,954,848.0</t>
-  </si>
-  <si>
-    <t>2,774,384.0</t>
-  </si>
-  <si>
-    <t>Top Traded Stocks</t>
-  </si>
-  <si>
-    <t>Turnover (Rs.)</t>
-  </si>
-  <si>
-    <t>Sub Indices</t>
-  </si>
-  <si>
-    <t>Turnover</t>
-  </si>
-  <si>
-    <t>Percentage (%)</t>
-  </si>
-  <si>
-    <t>266,245,361.1</t>
-  </si>
-  <si>
-    <t>65,593,080.1</t>
-  </si>
-  <si>
-    <t>61,326,748.8</t>
-  </si>
-  <si>
-    <t>56,379,605.5</t>
-  </si>
-  <si>
-    <t>56,278,592.0</t>
+    <t>163,566,724.8</t>
+  </si>
+  <si>
+    <t>146,979,601.19</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>1,105,737,971.0</t>
+    <t>1,448,703,353.9</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>834,801,319.4</t>
+    <t>1,234,988,754.9</t>
   </si>
   <si>
     <t>Commercial Banks</t>
   </si>
   <si>
-    <t>143,297,990.3</t>
+    <t>118,650,551.5</t>
+  </si>
+  <si>
+    <t>Hotels And Tourism</t>
+  </si>
+  <si>
+    <t>101,553,810.8</t>
+  </si>
+  <si>
+    <t>Non Life Insurance</t>
+  </si>
+  <si>
+    <t>98,606,163.6</t>
+  </si>
+  <si>
+    <t>Microfinance</t>
+  </si>
+  <si>
+    <t>94,134,153.3</t>
   </si>
   <si>
     <t>Development Banks</t>
   </si>
   <si>
-    <t>106,433,518.6</t>
-  </si>
-  <si>
-    <t>Non Life Insurance</t>
-  </si>
-  <si>
-    <t>91,075,070.0</t>
+    <t>89,168,691.0</t>
   </si>
   <si>
     <t>Investment</t>
   </si>
   <si>
-    <t>90,155,065.9</t>
-  </si>
-  <si>
-    <t>Hotels And Tourism</t>
-  </si>
-  <si>
-    <t>89,406,737.0</t>
-  </si>
-  <si>
-    <t>Microfinance</t>
-  </si>
-  <si>
-    <t>86,338,710.6</t>
+    <t>72,563,349.4</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>70,611,607.9</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>49,734,472.2</t>
+  </si>
+  <si>
+    <t>Life Insurance</t>
+  </si>
+  <si>
+    <t>36,626,858.6</t>
   </si>
   <si>
     <t>Manufacturing And Processing</t>
   </si>
   <si>
-    <t>69,614,462.5</t>
-  </si>
-  <si>
-    <t>Finance</t>
-  </si>
-  <si>
-    <t>68,121,459.9</t>
-  </si>
-  <si>
-    <t>Others</t>
-  </si>
-  <si>
-    <t>57,922,695.9</t>
-  </si>
-  <si>
-    <t>Life Insurance</t>
-  </si>
-  <si>
-    <t>49,279,137.7</t>
+    <t>27,205,248.5</t>
+  </si>
+  <si>
+    <t>Mutual Fund</t>
+  </si>
+  <si>
+    <t>23,055,757.34</t>
   </si>
   <si>
     <t>Trading</t>
   </si>
   <si>
-    <t>8,852,608.5</t>
-  </si>
-  <si>
-    <t>Mutual Fund</t>
-  </si>
-  <si>
-    <t>4,273,930.37</t>
+    <t>1,023,620.0</t>
   </si>
   <si>
     <t>Tradings</t>
   </si>
   <si>
-    <t>642,574.0</t>
+    <t>561,614.0</t>
   </si>
   <si>
     <t>Total</t>
@@ -632,211 +647,208 @@
     <t>100%</t>
   </si>
   <si>
-    <t>59,918,149.6</t>
-  </si>
-  <si>
-    <t>52,953,649.3</t>
-  </si>
-  <si>
-    <t>9,854,439.8</t>
-  </si>
-  <si>
-    <t>9,745,179.8</t>
-  </si>
-  <si>
-    <t>4,738,548.2</t>
-  </si>
-  <si>
-    <t>79,586,040.9</t>
-  </si>
-  <si>
-    <t>17,878,322.89</t>
-  </si>
-  <si>
-    <t>8,049,644.0</t>
-  </si>
-  <si>
-    <t>3,281,333.1</t>
-  </si>
-  <si>
-    <t>2,822,332.0</t>
-  </si>
-  <si>
-    <t>42,863,339.0</t>
-  </si>
-  <si>
-    <t>40,485,546.0</t>
-  </si>
-  <si>
-    <t>22,419,938.5</t>
-  </si>
-  <si>
-    <t>6,471,882.5</t>
-  </si>
-  <si>
-    <t>5,657,816.8</t>
-  </si>
-  <si>
-    <t>45,182,287.1</t>
-  </si>
-  <si>
-    <t>32,816,227.1</t>
-  </si>
-  <si>
-    <t>10,431,860.4</t>
-  </si>
-  <si>
-    <t>5,914,105.5</t>
-  </si>
-  <si>
-    <t>5,834,360.0</t>
-  </si>
-  <si>
-    <t>32,414,151.2</t>
-  </si>
-  <si>
-    <t>27,641,903.4</t>
-  </si>
-  <si>
-    <t>13,140,982.3</t>
-  </si>
-  <si>
-    <t>4,581,634.5</t>
-  </si>
-  <si>
-    <t>4,411,976.59</t>
-  </si>
-  <si>
-    <t>43,999,315.7</t>
-  </si>
-  <si>
-    <t>24,002,616.1</t>
-  </si>
-  <si>
-    <t>9,822,780.3</t>
-  </si>
-  <si>
-    <t>6,881,769.3</t>
-  </si>
-  <si>
-    <t>4,489,575.5</t>
-  </si>
-  <si>
-    <t>28,666,628.4</t>
-  </si>
-  <si>
-    <t>27,519,040.9</t>
-  </si>
-  <si>
-    <t>10,842,005.7</t>
-  </si>
-  <si>
-    <t>9,809,027.0</t>
-  </si>
-  <si>
-    <t>6,655,507.2</t>
-  </si>
-  <si>
-    <t>71,082,470.5</t>
-  </si>
-  <si>
-    <t>54,298,277.7</t>
-  </si>
-  <si>
-    <t>7,417,996.4</t>
-  </si>
-  <si>
-    <t>7,245,654.6</t>
-  </si>
-  <si>
-    <t>7,212,504.2</t>
-  </si>
-  <si>
-    <t>66,266,560.5</t>
-  </si>
-  <si>
-    <t>17,826,706.39</t>
-  </si>
-  <si>
-    <t>8,128,304.3</t>
-  </si>
-  <si>
-    <t>5,951,094.1</t>
-  </si>
-  <si>
-    <t>5,476,170.0</t>
-  </si>
-  <si>
-    <t>41,778,068.6</t>
-  </si>
-  <si>
-    <t>36,874,096.29</t>
-  </si>
-  <si>
-    <t>4,505,238.9</t>
-  </si>
-  <si>
-    <t>3,784,853.1</t>
-  </si>
-  <si>
-    <t>41,374,497.0</t>
-  </si>
-  <si>
-    <t>39,393,319.7</t>
-  </si>
-  <si>
-    <t>7,256,591.9</t>
-  </si>
-  <si>
-    <t>5,693,664.8</t>
-  </si>
-  <si>
-    <t>4,711,595.9</t>
-  </si>
-  <si>
-    <t>70,409,352.2</t>
-  </si>
-  <si>
-    <t>24,030,568.1</t>
-  </si>
-  <si>
-    <t>8,391,186.6</t>
-  </si>
-  <si>
-    <t>2,475,228.6</t>
-  </si>
-  <si>
-    <t>1,965,651.4</t>
-  </si>
-  <si>
-    <t>38,429,052.79</t>
-  </si>
-  <si>
-    <t>20,354,823.7</t>
-  </si>
-  <si>
-    <t>11,845,098.0</t>
-  </si>
-  <si>
-    <t>7,561,243.9</t>
-  </si>
-  <si>
-    <t>3,779,684.3</t>
-  </si>
-  <si>
-    <t>31,251,998.0</t>
-  </si>
-  <si>
-    <t>19,908,804.3</t>
-  </si>
-  <si>
-    <t>8,327,057.8</t>
-  </si>
-  <si>
-    <t>4,527,440.7</t>
-  </si>
-  <si>
-    <t>4,150,857.3</t>
+    <t>54,103,960.4</t>
+  </si>
+  <si>
+    <t>23,253,751.4</t>
+  </si>
+  <si>
+    <t>4,062,670.0</t>
+  </si>
+  <si>
+    <t>1,000,557.5</t>
+  </si>
+  <si>
+    <t>957,428.1</t>
+  </si>
+  <si>
+    <t>66,257,097.6</t>
+  </si>
+  <si>
+    <t>22,377,040.8</t>
+  </si>
+  <si>
+    <t>20,102,342.2</t>
+  </si>
+  <si>
+    <t>17,346,275.1</t>
+  </si>
+  <si>
+    <t>2,537,968.0</t>
+  </si>
+  <si>
+    <t>70,311,623.9</t>
+  </si>
+  <si>
+    <t>52,853,109.0</t>
+  </si>
+  <si>
+    <t>19,573,168.0</t>
+  </si>
+  <si>
+    <t>18,024,124.3</t>
+  </si>
+  <si>
+    <t>1,778,182.9</t>
+  </si>
+  <si>
+    <t>99,061,700.4</t>
+  </si>
+  <si>
+    <t>50,078,769.9</t>
+  </si>
+  <si>
+    <t>5,996,861.3</t>
+  </si>
+  <si>
+    <t>1,678,211.5</t>
+  </si>
+  <si>
+    <t>1,133,488.89</t>
+  </si>
+  <si>
+    <t>123,988,839.9</t>
+  </si>
+  <si>
+    <t>18,418,614.89</t>
+  </si>
+  <si>
+    <t>1,370,613.0</t>
+  </si>
+  <si>
+    <t>702,458.0</t>
+  </si>
+  <si>
+    <t>126,541,159.5</t>
+  </si>
+  <si>
+    <t>38,631,456.9</t>
+  </si>
+  <si>
+    <t>2,479,105.0</t>
+  </si>
+  <si>
+    <t>606,378.0</t>
+  </si>
+  <si>
+    <t>488,470.0</t>
+  </si>
+  <si>
+    <t>54,588,329.0</t>
+  </si>
+  <si>
+    <t>23,285,897.8</t>
+  </si>
+  <si>
+    <t>15,737,668.0</t>
+  </si>
+  <si>
+    <t>2,655,445.0</t>
+  </si>
+  <si>
+    <t>1,748,700.0</t>
+  </si>
+  <si>
+    <t>244,208,387.7</t>
+  </si>
+  <si>
+    <t>68,025,740.4</t>
+  </si>
+  <si>
+    <t>2,042,506.4</t>
+  </si>
+  <si>
+    <t>1,556,001.8</t>
+  </si>
+  <si>
+    <t>508,188.0</t>
+  </si>
+  <si>
+    <t>102,074,579.2</t>
+  </si>
+  <si>
+    <t>26,375,963.9</t>
+  </si>
+  <si>
+    <t>21,944,234.0</t>
+  </si>
+  <si>
+    <t>8,174,202.0</t>
+  </si>
+  <si>
+    <t>7,138,929.9</t>
+  </si>
+  <si>
+    <t>72,023,349.59</t>
+  </si>
+  <si>
+    <t>27,542,830.3</t>
+  </si>
+  <si>
+    <t>2,133,713.9</t>
+  </si>
+  <si>
+    <t>1,380,028.0</t>
+  </si>
+  <si>
+    <t>501,116.1</t>
+  </si>
+  <si>
+    <t>49,519,156.6</t>
+  </si>
+  <si>
+    <t>36,385,825.7</t>
+  </si>
+  <si>
+    <t>4,018,046.4</t>
+  </si>
+  <si>
+    <t>2,126,089.7</t>
+  </si>
+  <si>
+    <t>54,425,826.6</t>
+  </si>
+  <si>
+    <t>21,361,433.89</t>
+  </si>
+  <si>
+    <t>12,922,192.0</t>
+  </si>
+  <si>
+    <t>1,481,080.5</t>
+  </si>
+  <si>
+    <t>584,314.3</t>
+  </si>
+  <si>
+    <t>33,883,732.4</t>
+  </si>
+  <si>
+    <t>32,150,286.3</t>
+  </si>
+  <si>
+    <t>2,693,732.7</t>
+  </si>
+  <si>
+    <t>2,561,948.9</t>
+  </si>
+  <si>
+    <t>2,297,477.6</t>
+  </si>
+  <si>
+    <t>54,489,348.0</t>
+  </si>
+  <si>
+    <t>34,439,911.6</t>
+  </si>
+  <si>
+    <t>25,762,713.0</t>
+  </si>
+  <si>
+    <t>21,202,013.1</t>
+  </si>
+  <si>
+    <t>4,333,522.4</t>
   </si>
 </sst>
 </file>
@@ -1645,61 +1657,61 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.03006083590668958</v>
+        <v>0.07645406585062989</v>
       </c>
       <c r="E9" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>65</v>
-      </c>
       <c r="G9" s="12">
-        <v>0.159275562376415</v>
+        <v>0.1304349123360146</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J9" s="14">
-        <v>0.04149391511160899</v>
+        <v>0.1949112425363745</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M9" s="16">
-        <v>0.03601274202521984</v>
+        <v>0.1513128488532149</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="P9" s="18">
-        <v>0.04832438228279218</v>
+        <v>0.482380933197789</v>
       </c>
       <c r="Q9" s="15" t="s">
         <v>96</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="S9" s="16">
-        <v>0.04487913669640632</v>
+        <v>0.2720677468633469</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="V9" s="18">
-        <v>0.04436703312024017</v>
+        <v>0.2232702711085532</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1711,61 +1723,61 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.02754261771165211</v>
+        <v>0.0457938730193615</v>
       </c>
       <c r="E10" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>67</v>
-      </c>
       <c r="G10" s="12">
-        <v>0.08671486191636309</v>
+        <v>0.07198960976744755</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J10" s="14">
-        <v>0.02604642073995242</v>
+        <v>0.1230944330240877</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M10" s="16">
-        <v>0.03307819437830492</v>
+        <v>0.1404934205676644</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="P10" s="18">
-        <v>0.01975535897654901</v>
+        <v>0.07050986032461103</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="R10" s="15" t="s">
         <v>99</v>
       </c>
       <c r="S10" s="16">
-        <v>0.02254260188317709</v>
+        <v>0.154644632047078</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="V10" s="18">
-        <v>0.02659559164404913</v>
+        <v>0.06228982543062447</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1777,43 +1789,43 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.02728689614192019</v>
+        <v>0.04041511883690957</v>
       </c>
       <c r="E11" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="F11" s="11" t="s">
-        <v>69</v>
-      </c>
       <c r="G11" s="12">
-        <v>0.01939275335306626</v>
+        <v>0.06336429848381228</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J11" s="14">
-        <v>0.02503822396952282</v>
+        <v>0.1081330070228549</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="M11" s="16">
-        <v>0.02740925687080851</v>
+        <v>0.1362470972637446</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="P11" s="18">
-        <v>0.01841729898714186</v>
+        <v>0.0477158767933528</v>
       </c>
       <c r="Q11" s="15" t="s">
         <v>100</v>
@@ -1822,16 +1834,16 @@
         <v>101</v>
       </c>
       <c r="S11" s="16">
-        <v>0.01983195342560938</v>
+        <v>0.1318482076592475</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="V11" s="18">
-        <v>0.02515098735694644</v>
+        <v>0.04831930489911781</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1843,61 +1855,61 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.02570114915417436</v>
+        <v>0.009803451481660057</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G12" s="12">
-        <v>0.01739628274427679</v>
+        <v>0.04941743176884099</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J12" s="14">
-        <v>0.0233887169431512</v>
+        <v>0.06955703056632506</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="M12" s="16">
-        <v>0.02495984210115628</v>
+        <v>0.07720053967232665</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P12" s="18">
-        <v>0.01841529131735054</v>
+        <v>0.009166168393774677</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="S12" s="16">
-        <v>0.01814756313357608</v>
+        <v>0.04510467486396091</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="V12" s="18">
-        <v>0.02458933820853726</v>
+        <v>0.02939188650661142</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1909,61 +1921,61 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.01682814929020934</v>
+        <v>0.004778396401477704</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G13" s="12">
-        <v>0.01053864587948823</v>
+        <v>0.03537918226208512</v>
       </c>
       <c r="H13" s="13" t="s">
         <v>58</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J13" s="14">
-        <v>0.02215514901613997</v>
+        <v>0.04596855226763868</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="M13" s="16">
-        <v>0.02313115647677655</v>
+        <v>0.01295909144561793</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="P13" s="18">
-        <v>0.01570994858935143</v>
+        <v>0.002788202075712279</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="S13" s="16">
-        <v>0.01791687254782108</v>
+        <v>0.01536465164369463</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="V13" s="18">
-        <v>0.02188821793877718</v>
+        <v>0.01067018672676878</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1974,7 +1986,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -1983,7 +1995,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -1992,7 +2004,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -2001,7 +2013,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -2010,7 +2022,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -2019,7 +2031,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -2028,7 +2040,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -2037,566 +2049,566 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D16" s="10">
-        <v>0.04478080670103528</v>
+        <v>0.5590466391621324</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G16" s="12">
-        <v>0.1757408622343529</v>
+        <v>0.1816772339455011</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="J16" s="14">
-        <v>0.03344689422812462</v>
+        <v>0.144253121172472</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>66</v>
+        <v>138</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M16" s="16">
-        <v>0.06597732910824686</v>
+        <v>0.08435988003288798</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="P16" s="18">
-        <v>0.2476174123121147</v>
+        <v>0.153919522129313</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="S16" s="16">
-        <v>0.05377921107505178</v>
+        <v>0.1253750710106221</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>156</v>
+        <v>106</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="V16" s="18">
-        <v>0.02942555427947195</v>
+        <v>0.2225449087217742</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D17" s="10">
-        <v>0.0318453036647202</v>
+        <v>0.1163231028788008</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G17" s="12">
-        <v>0.02567917655032855</v>
+        <v>0.06511473722942759</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J17" s="14">
-        <v>0.02464032029786052</v>
+        <v>0.1021744684285036</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="M17" s="16">
-        <v>0.03120054817923559</v>
+        <v>0.06862139502692262</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="P17" s="18">
-        <v>0.0116863953040597</v>
+        <v>0.07299682507347065</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>151</v>
+        <v>98</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="S17" s="16">
-        <v>0.03352726683561496</v>
+        <v>0.06260823914852945</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="V17" s="18">
-        <v>0.02889170310949078</v>
+        <v>0.1268816280669939</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>58</v>
+        <v>119</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D18" s="10">
-        <v>0.02982755538433031</v>
+        <v>0.0252827244663885</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G18" s="12">
-        <v>0.01944390305601717</v>
+        <v>0.06090567243718988</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>96</v>
+        <v>133</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="J18" s="14">
-        <v>0.02428017429675506</v>
+        <v>0.06140705469603445</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M18" s="16">
-        <v>0.02223144125384329</v>
+        <v>0.03482037582974485</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="P18" s="18">
-        <v>0.01009570562826652</v>
+        <v>0.05181449259798657</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>66</v>
+        <v>155</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="S18" s="16">
-        <v>0.02961483561188408</v>
+        <v>0.03267099717939412</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>106</v>
+        <v>162</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="V18" s="18">
-        <v>0.02648563857257712</v>
+        <v>0.08575762030986997</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>116</v>
+        <v>62</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D19" s="10">
-        <v>0.02007334226637831</v>
+        <v>0.0217383153603694</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G19" s="12">
-        <v>0.01781132253876692</v>
+        <v>0.05949907627629974</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="J19" s="14">
-        <v>0.01702826536704531</v>
+        <v>0.01662350791228081</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="M19" s="16">
-        <v>0.02173739974728797</v>
+        <v>0.03367218909971913</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="P19" s="18">
-        <v>0.01001881480922307</v>
+        <v>0.04692053700346326</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="S19" s="16">
-        <v>0.02157480697664733</v>
+        <v>0.009680798034941908</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="V19" s="18">
-        <v>0.01638581251237711</v>
+        <v>0.07281431334506756</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D20" s="10">
-        <v>0.01819329629667737</v>
+        <v>0.009504912150567911</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>125</v>
+        <v>58</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G20" s="12">
-        <v>0.01598128655542369</v>
+        <v>0.02612413252515257</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>133</v>
+        <v>62</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J20" s="14">
-        <v>0.01679403716575868</v>
+        <v>0.009109878113158396</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="M20" s="16">
-        <v>0.01631141632116301</v>
+        <v>0.02077290821103274</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="P20" s="18">
-        <v>0.009276149764325763</v>
+        <v>0.004647881860683084</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="S20" s="16">
-        <v>0.01975648812148893</v>
+        <v>0.009094764997767558</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="V20" s="18">
-        <v>0.01538506754369052</v>
+        <v>0.03281274095041647</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="24" spans="1:22">
       <c r="B24" s="20" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>70</v>
+        <v>174</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>100</v>
+        <v>155</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="D31" s="22">
-        <v>0.3889950497353945</v>
+        <v>0.5096491646140308</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="D32" s="22">
-        <v>0.2936804100753594</v>
+        <v>0.4344650583903829</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D33" s="22">
-        <v>0.05041177053304845</v>
+        <v>0.04174088110597631</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="D34" s="22">
-        <v>0.03744296835883918</v>
+        <v>0.03572630290270175</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D35" s="22">
-        <v>0.03203991570648932</v>
+        <v>0.03468933013045497</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="D36" s="22">
-        <v>0.03171626123316721</v>
+        <v>0.03311609133908702</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D37" s="22">
-        <v>0.03145300154117104</v>
+        <v>0.03136925772659843</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D38" s="22">
-        <v>0.03037367975485471</v>
+        <v>0.02552755214084966</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D39" s="22">
-        <v>0.02449014324614367</v>
+        <v>0.02484093577985365</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D40" s="22">
-        <v>0.02396490974971518</v>
+        <v>0.0174964268157547</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="D41" s="22">
-        <v>0.02037701748819534</v>
+        <v>0.0128852106524596</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="D42" s="22">
-        <v>0.01733624160812042</v>
+        <v>0.009570718624911241</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="D43" s="22">
-        <v>0.003114319100963094</v>
+        <v>0.008110941026154275</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="D44" s="22">
-        <v>0.001503554911241954</v>
+        <v>0.0003601062125505542</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="D45" s="22">
-        <v>0.0002260554594707604</v>
+        <v>0.0001975739927466901</v>
       </c>
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="20" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -2975,331 +2987,331 @@
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D9" s="10">
-        <v>0.1814781468768419</v>
+        <v>0.1336044228916231</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="G9" s="12">
-        <v>0.3313771298037318</v>
+        <v>0.2159637093105701</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="J9" s="14">
-        <v>0.1807563251572882</v>
+        <v>0.2593333620795384</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="M9" s="16">
-        <v>0.2020136744629448</v>
+        <v>0.3716673758121805</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="P9" s="18">
-        <v>0.1509554910127621</v>
+        <v>0.4984528197704265</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="S9" s="16">
-        <v>0.216501707694111</v>
+        <v>0.5142869628040272</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="V9" s="18">
-        <v>0.1589679057347061</v>
+        <v>0.2240536002632199</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="D10" s="10">
-        <v>0.1603842943996751</v>
+        <v>0.05742285801063601</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="G10" s="12">
-        <v>0.07444103590666651</v>
+        <v>0.07293752533105173</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="J10" s="14">
-        <v>0.1707290819538429</v>
+        <v>0.1949403767550632</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="M10" s="16">
-        <v>0.14672401606871</v>
+        <v>0.1878894155610013</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="P10" s="18">
-        <v>0.1287307224097338</v>
+        <v>0.07404545877334716</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="S10" s="16">
-        <v>0.1181065498883694</v>
+        <v>0.1570054732886787</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="V10" s="18">
-        <v>0.1526040746284876</v>
+        <v>0.09557517757049114</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="D11" s="10">
-        <v>0.02984680744235461</v>
+        <v>0.01003236503827381</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="G11" s="12">
-        <v>0.03351678126586934</v>
+        <v>0.06552318988603578</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="J11" s="14">
-        <v>0.0945457304087394</v>
+        <v>0.07219255056897689</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="M11" s="16">
-        <v>0.04664169492403772</v>
+        <v>0.02249948964615815</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>227</v>
+        <v>92</v>
       </c>
       <c r="P11" s="18">
-        <v>0.06119868520532218</v>
+        <v>0.0477158767933528</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="S11" s="16">
-        <v>0.04833367690884502</v>
+        <v>0.01007554684942078</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="V11" s="18">
-        <v>0.06012325258636785</v>
+        <v>0.06459404857670706</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D12" s="10">
-        <v>0.0295158843003662</v>
+        <v>0.002470778596780601</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="G12" s="12">
-        <v>0.01366268170035308</v>
+        <v>0.05653984326227988</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="J12" s="14">
-        <v>0.02729217379798068</v>
+        <v>0.06647914660464138</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="M12" s="16">
-        <v>0.026442445920727</v>
+        <v>0.006296444152929391</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="P12" s="18">
-        <v>0.02133706606479058</v>
+        <v>0.005510059737755508</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="S12" s="16">
-        <v>0.03386222675746993</v>
+        <v>0.002464433715981403</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="V12" s="18">
-        <v>0.05439497305812172</v>
+        <v>0.01089906988270269</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="D13" s="10">
-        <v>0.01435196099951983</v>
+        <v>0.002364274774249673</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="G13" s="12">
-        <v>0.01175151153313905</v>
+        <v>0.008272456887570169</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="J13" s="14">
-        <v>0.02385922788659017</v>
+        <v>0.006558547851279873</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="M13" s="16">
-        <v>0.02608589731482687</v>
+        <v>0.004252711625927582</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="P13" s="18">
-        <v>0.02054695462733008</v>
+        <v>0.002823981345036315</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="S13" s="16">
-        <v>0.02209126999153858</v>
+        <v>0.001985233529655489</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="V13" s="18">
-        <v>0.03690744605271605</v>
+        <v>0.007177404730236248</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3310,7 +3322,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -3319,7 +3331,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -3328,7 +3340,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -3337,7 +3349,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -3346,7 +3358,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -3355,7 +3367,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -3364,7 +3376,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -3373,331 +3385,331 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D16" s="10">
-        <v>0.2152922796829457</v>
+        <v>0.6030486578567039</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="G16" s="12">
-        <v>0.2759180174328202</v>
+        <v>0.3327100876562931</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="J16" s="14">
-        <v>0.176179698746873</v>
+        <v>0.2656467930048473</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="M16" s="16">
-        <v>0.1849887357301593</v>
+        <v>0.1857898149500613</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="P16" s="18">
-        <v>0.3279024111308984</v>
+        <v>0.2187995851802972</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="S16" s="16">
-        <v>0.1890928398294876</v>
+        <v>0.1377098320682008</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="V16" s="18">
-        <v>0.1733048129261418</v>
+        <v>0.2236473403572306</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D17" s="10">
-        <v>0.1644568612579476</v>
+        <v>0.1679828929476551</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="G17" s="12">
-        <v>0.07422611721706859</v>
+        <v>0.08597193669536304</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="J17" s="14">
-        <v>0.1554994616887863</v>
+        <v>0.1015873960334627</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="M17" s="16">
-        <v>0.1761307311486343</v>
+        <v>0.1365151647919663</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="P17" s="18">
-        <v>0.1119124232027127</v>
+        <v>0.08587601086018855</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="S17" s="16">
-        <v>0.1001573324664811</v>
+        <v>0.1306647825880474</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="V17" s="18">
-        <v>0.1104022726737237</v>
+        <v>0.1413559698214435</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D18" s="10">
-        <v>0.02246738674672097</v>
+        <v>0.005043769195580861</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="G18" s="12">
-        <v>0.03384430383325339</v>
+        <v>0.07152680006042295</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>130</v>
+        <v>256</v>
       </c>
       <c r="J18" s="14">
-        <v>0.02428017429675506</v>
+        <v>0.007869868006317572</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>256</v>
+        <v>143</v>
       </c>
       <c r="M18" s="16">
-        <v>0.03244481162612598</v>
+        <v>0.03482037582974485</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="P18" s="18">
-        <v>0.03907847796374535</v>
+        <v>0.05194905481178591</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="S18" s="16">
-        <v>0.05828463247677506</v>
+        <v>0.01094783400407274</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="V18" s="18">
-        <v>0.04617686185229405</v>
+        <v>0.10574107517008</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D19" s="10">
-        <v>0.02194540349619984</v>
+        <v>0.003842393809443325</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="G19" s="12">
-        <v>0.02477892429060285</v>
+        <v>0.02664365099768392</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="J19" s="14">
-        <v>0.01899876319760492</v>
+        <v>0.00509001614744246</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="M19" s="16">
-        <v>0.025456837651061</v>
+        <v>0.01507521832705769</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="P19" s="18">
-        <v>0.01152735255587479</v>
+        <v>0.005954154842705268</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="S19" s="16">
-        <v>0.03720562901030935</v>
+        <v>0.01041223996876778</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="V19" s="18">
-        <v>0.02510646722643783</v>
+        <v>0.08702203300421509</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D20" s="10">
-        <v>0.02184499864056949</v>
+        <v>0.001254920415409149</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="G20" s="12">
-        <v>0.02280145458168283</v>
+        <v>0.0232692019052784</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="J20" s="14">
-        <v>0.01596086897514378</v>
+        <v>0.001848287890349609</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="M20" s="16">
-        <v>0.02106592785435922</v>
+        <v>0.007976828343846054</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="P20" s="18">
-        <v>0.009154207692068867</v>
+        <v>0.002349026821301705</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="S20" s="16">
-        <v>0.01859820073280414</v>
+        <v>0.009337379092170289</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="V20" s="18">
-        <v>0.02301816184231197</v>
+        <v>0.01778660957988491</v>
       </c>
     </row>
   </sheetData>
